--- a/10_DRAWINGS/for_OMi_2026-10-20/AirWay_values_to_confirm_2026-10-20.xlsx
+++ b/10_DRAWINGS/for_OMi_2026-10-20/AirWay_values_to_confirm_2026-10-20.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Air-Way values to confirm" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Air-Way values to confirm" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,8 +517,11 @@
           <t>differs from Brennan / OMi website by 0.180 in</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -552,8 +555,11 @@
           <t>differs from Brennan / OMi website by 0.180 in</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -587,8 +593,11 @@
           <t>differs from Brennan / OMi website by 0.188 in</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -622,8 +631,11 @@
           <t>differs from Brennan / OMi website by 0.188 in</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -657,8 +669,11 @@
           <t>Air-Way's forged (-FG) length is much longer than its plain part of the same size</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -692,8 +707,11 @@
           <t>Air-Way's forged (-FG) length is much longer than its plain part of the same size</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -727,8 +745,11 @@
           <t>differs from Brennan / OMi website by 0.188 in</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -762,8 +783,11 @@
           <t>differs from Brennan / OMi website by 0.185 in</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -797,8 +821,11 @@
           <t>differs from Brennan / OMi website by 0.185 in</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -832,8 +859,11 @@
           <t>differs from Brennan / OMi website by 0.318 in</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -867,8 +897,11 @@
           <t>differs from Brennan / OMi website by 0.210 in</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -902,8 +935,11 @@
           <t>differs from Brennan / OMi website by 0.480 in</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -937,8 +973,11 @@
           <t>Air-Way's bore equals the pipe tap drill - looks like the tap-drill column printed in the bore column</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -972,8 +1011,11 @@
           <t>Air-Way's bore equals the pipe tap drill - looks like the tap-drill column printed in the bore column</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1007,8 +1049,11 @@
           <t>Air-Way's bore equals the pipe tap drill - looks like the tap-drill column printed in the bore column</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1042,8 +1087,11 @@
           <t>Air-Way's bore equals the pipe tap drill - looks like the tap-drill column printed in the bore column</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1077,8 +1125,11 @@
           <t>Air-Way's bore equals the pipe tap drill - looks like the tap-drill column printed in the bore column</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1112,8 +1163,11 @@
           <t>Air-Way's bore equals the pipe tap drill - looks like the tap-drill column printed in the bore column</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1147,8 +1201,11 @@
           <t>Air-Way's 6405 lengths were flagged as suspect in our first build (2026-09); differs from Brennan / OMi website by 0.290 in</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1182,8 +1239,11 @@
           <t>Air-Way's 6405 lengths were flagged as suspect in our first build (2026-09); differs from Brennan / OMi website by 0.160 in</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1217,8 +1277,11 @@
           <t>Air-Way's 6405 lengths were flagged as suspect in our first build (2026-09); differs from Brennan / OMi website by 0.400 in</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1252,8 +1315,11 @@
           <t>Air-Way's 6405 lengths were flagged as suspect in our first build (2026-09); differs from Brennan / OMi website by 0.180 in</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1287,8 +1353,11 @@
           <t>Air-Way prints exactly 1.00 - looks like a filler value</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1322,8 +1391,11 @@
           <t>Air-Way's 6405 lengths were flagged as suspect in our first build (2026-09); differs from Brennan / OMi website by 0.250 in</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1357,8 +1429,11 @@
           <t>Air-Way's 6405 lengths were flagged as suspect in our first build (2026-09); differs from Brennan / OMi website by 0.180 in</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1392,8 +1467,11 @@
           <t>Air-Way prints exactly 1.00 - looks like a filler value</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1427,8 +1505,11 @@
           <t>Air-Way's 6405 lengths were flagged as suspect in our first build (2026-09); differs from Brennan / OMi website by 0.310 in</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1462,8 +1543,11 @@
           <t>Air-Way's 6405 lengths were flagged as suspect in our first build (2026-09); differs from Brennan / OMi website by 0.160 in</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1497,8 +1581,11 @@
           <t>Air-Way's 6405 lengths were flagged as suspect in our first build (2026-09); differs from Brennan / OMi website by 0.570 in</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1532,8 +1619,11 @@
           <t>Air-Way's 6405 lengths were flagged as suspect in our first build (2026-09); differs from Brennan / OMi website by 0.570 in</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1567,8 +1657,11 @@
           <t>differs from Brennan / OMi website by 0.300 in</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1602,8 +1695,11 @@
           <t>differs from Brennan / OMi website by 0.390 in</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1637,8 +1733,11 @@
           <t>differs from Brennan / OMi website by 0.450 in</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1672,8 +1771,11 @@
           <t>Air-Way value out of step with the neighbouring sizes (likely typo)</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1707,8 +1809,11 @@
           <t>differs from Brennan / OMi website by 0.180 in</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1742,8 +1847,11 @@
           <t>differs from Brennan / OMi website by 0.180 in</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1777,8 +1885,11 @@
           <t>differs from Brennan / OMi website by 0.180 in</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1812,8 +1923,11 @@
           <t>differs from Brennan / OMi website by 0.180 in</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1847,8 +1961,11 @@
           <t>differs from Brennan / OMi website by 0.170 in</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1882,8 +1999,11 @@
           <t>differs from Brennan / OMi website by 0.170 in</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>not settled by the PDFs: no drawing of this configuration (PDFs = -08 sizes only) - keep, ask Triveni</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
